--- a/docs/FYI.xlsx
+++ b/docs/FYI.xlsx
@@ -1,22 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ZAHID\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Others\NGGL\biman-ui\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4DA8024C-A1C2-43FB-942B-3273DB4BA70F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{762C2D65-A984-4F00-99A4-61140B207435}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="22785" windowHeight="14535"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -174,7 +172,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -734,25 +732,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B23DAC8B-B965-4CD3-A634-F5597E3F0874}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A3:L35"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.1796875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.7265625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="24.90625" customWidth="1"/>
-    <col min="10" max="10" width="13.26953125" customWidth="1"/>
-    <col min="11" max="11" width="11.90625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.5703125" customWidth="1"/>
+    <col min="9" max="9" width="56.42578125" customWidth="1"/>
+    <col min="10" max="10" width="32" customWidth="1"/>
+    <col min="11" max="11" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:12" s="9" customFormat="1" ht="116" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:12" s="9" customFormat="1" ht="135" x14ac:dyDescent="0.25">
       <c r="A3" s="6" t="s">
         <v>10</v>
       </c>
@@ -784,7 +782,7 @@
       <c r="K3" s="6"/>
       <c r="L3" s="6"/>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>11</v>
       </c>
@@ -816,7 +814,7 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" spans="1:12" ht="20" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:12" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -836,7 +834,7 @@
       <c r="K5" s="4"/>
       <c r="L5" s="5"/>
     </row>
-    <row r="6" spans="1:12" ht="20" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:12" ht="19.5" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -856,10 +854,10 @@
       <c r="K6" s="2"/>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="I7" s="1"/>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="I10" s="11" t="s">
         <v>30</v>
       </c>
@@ -867,7 +865,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="I11" t="s">
         <v>27</v>
       </c>
@@ -875,7 +873,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="I12" t="s">
         <v>28</v>
       </c>
@@ -883,7 +881,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="I13" t="s">
         <v>29</v>
       </c>
@@ -891,7 +889,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="I14" t="s">
         <v>36</v>
       </c>
@@ -899,7 +897,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="I15" t="s">
         <v>32</v>
       </c>
@@ -910,7 +908,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:9" x14ac:dyDescent="0.25">
       <c r="E19" s="12" t="s">
         <v>25</v>
       </c>
@@ -921,24 +919,24 @@
         <v>35</v>
       </c>
     </row>
-    <row r="20" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:9" x14ac:dyDescent="0.25">
       <c r="I20" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B21" s="12" t="s">
         <v>24</v>
       </c>
       <c r="C21" s="12"/>
       <c r="D21" s="12"/>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
       <c r="I22" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="35" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="13" t="s">
         <v>26</v>
       </c>
@@ -955,13 +953,4 @@
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F487F7C-4B73-4A51-A422-38D9E50D8451}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>